--- a/data/trans_camb/P1_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,35</t>
+          <t>-0,01; 5,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,87</t>
+          <t>3,76; 9,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 23,57</t>
+          <t>16,02; 23,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,1</t>
+          <t>0,07; 6,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,22</t>
+          <t>2,19; 8,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,77</t>
+          <t>7,4; 14,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,98</t>
+          <t>0,93; 4,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,22</t>
+          <t>3,82; 8,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,4; 17,83</t>
+          <t>12,05; 17,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 120,33</t>
+          <t>-2,41; 123,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,9; 222,37</t>
+          <t>54,62; 226,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>220,41; 545,62</t>
+          <t>230,04; 570,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 105,07</t>
+          <t>-0,46; 105,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,15; 133,15</t>
+          <t>26,15; 149,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,04; 253,27</t>
+          <t>90,05; 260,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 90,31</t>
+          <t>12,86; 92,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>57,42; 151,26</t>
+          <t>53,18; 156,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>173,42; 329,43</t>
+          <t>172,2; 337,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,94</t>
+          <t>-0,67; 4,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,2</t>
+          <t>2,36; 7,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 10,99</t>
+          <t>-0,38; 10,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,57</t>
+          <t>-3,17; 1,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,6</t>
+          <t>-1,03; 4,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,63</t>
+          <t>5,09; 10,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,36</t>
+          <t>-1,16; 2,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,22</t>
+          <t>1,68; 5,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,8</t>
+          <t>1,59; 9,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 84,9</t>
+          <t>-10,41; 87,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,22; 161,58</t>
+          <t>32,47; 157,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 216,37</t>
+          <t>-0,84; 205,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 23,39</t>
+          <t>-35,05; 23,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 66,66</t>
+          <t>-11,08; 69,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,65; 156,84</t>
+          <t>51,21; 155,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 38,67</t>
+          <t>-15,19; 39,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 88,07</t>
+          <t>22,23; 87,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,2; 152,71</t>
+          <t>32,25; 155,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,35</t>
+          <t>-2,36; 3,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,77</t>
+          <t>2,19; 9,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,28</t>
+          <t>4,81; 11,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,68</t>
+          <t>-5,08; 1,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,64</t>
+          <t>-1,45; 5,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 4,37</t>
+          <t>-6,33; 4,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,51</t>
+          <t>-2,83; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,95</t>
+          <t>1,3; 5,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 6,49</t>
+          <t>-0,78; 6,73</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 51,74</t>
+          <t>-26,39; 58,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,57; 137,67</t>
+          <t>20,73; 143,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,91; 202,47</t>
+          <t>50,86; 192,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 19,84</t>
+          <t>-40,88; 14,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 64,92</t>
+          <t>-12,16; 60,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 45,39</t>
+          <t>-51,89; 44,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 18,97</t>
+          <t>-27,79; 22,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,69; 76,85</t>
+          <t>13,17; 76,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 79,73</t>
+          <t>-5,49; 80,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,12</t>
+          <t>-3,18; 2,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,87</t>
+          <t>1,36; 7,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 10,91</t>
+          <t>4,17; 10,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,49</t>
+          <t>0,63; 6,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,52</t>
+          <t>5,14; 11,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 13,05</t>
+          <t>6,24; 13,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,68</t>
+          <t>-0,11; 3,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,88</t>
+          <t>4,49; 8,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 11,07</t>
+          <t>6,3; 11,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 24,66</t>
+          <t>-28,72; 30,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,77; 87,26</t>
+          <t>13,04; 90,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,01; 128,54</t>
+          <t>37,57; 124,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,26; 77,94</t>
+          <t>5,89; 77,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,75; 139,03</t>
+          <t>47,33; 138,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,56; 157,52</t>
+          <t>62,87; 164,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 41,33</t>
+          <t>-1,08; 41,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,21; 99,4</t>
+          <t>41,8; 100,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>57,51; 128,93</t>
+          <t>60,15; 125,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,47</t>
+          <t>-0,31; 2,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,94</t>
+          <t>3,6; 6,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,56</t>
+          <t>5,65; 11,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,59</t>
+          <t>-0,2; 2,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,0</t>
+          <t>2,95; 6,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,3</t>
+          <t>4,24; 9,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,06</t>
+          <t>0,14; 2,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,85</t>
+          <t>3,78; 5,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,98</t>
+          <t>6,23; 9,87</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 36,48</t>
+          <t>-3,77; 37,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47,33; 102,2</t>
+          <t>43,69; 99,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74,99; 171,77</t>
+          <t>77,09; 173,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 32,41</t>
+          <t>-2,34; 33,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,85; 75,35</t>
+          <t>32,11; 76,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,84; 112,7</t>
+          <t>49,65; 113,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,53; 26,89</t>
+          <t>1,68; 28,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>44,27; 77,23</t>
+          <t>44,08; 77,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>74,99; 130,52</t>
+          <t>75,34; 128,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19,48</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,76</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,42</t>
+          <t>15,91</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,47</t>
+          <t>0,13; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,84</t>
+          <t>3,94; 9,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 23,76</t>
+          <t>15,36; 23,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,08</t>
+          <t>0,4; 6,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,41</t>
+          <t>1,91; 8,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,83</t>
+          <t>9,79; 15,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,97</t>
+          <t>0,88; 4,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,33</t>
+          <t>3,74; 8,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,95</t>
+          <t>13,35; 18,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>354,22%</t>
+          <t>349,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>165,5%</t>
+          <t>179,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>244,83%</t>
+          <t>252,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 123,33</t>
+          <t>-0,29; 128,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,62; 226,44</t>
+          <t>54,48; 227,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230,04; 570,6</t>
+          <t>215,51; 550,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 105,62</t>
+          <t>2,19; 112,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,15; 149,52</t>
+          <t>18,94; 144,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,05; 260,53</t>
+          <t>110,08; 267,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 92,91</t>
+          <t>11,42; 91,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,18; 156,95</t>
+          <t>52,46; 152,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>172,2; 337,66</t>
+          <t>179,3; 348,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>10,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>9,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,1</t>
+          <t>-0,66; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,43</t>
+          <t>2,26; 7,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 10,83</t>
+          <t>7,97; 13,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,62</t>
+          <t>-3,23; 1,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,56</t>
+          <t>-0,75; 4,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,27</t>
+          <t>5,17; 10,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,27</t>
+          <t>-0,99; 2,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,22</t>
+          <t>1,53; 5,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,57</t>
+          <t>7,35; 11,13</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116,44%</t>
+          <t>189,11%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>100,79%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>104,43%</t>
+          <t>135,84%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 87,85</t>
+          <t>-11,18; 90,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,47; 157,26</t>
+          <t>30,64; 159,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 205,31</t>
+          <t>112,61; 304,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 23,73</t>
+          <t>-34,43; 27,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 69,1</t>
+          <t>-8,22; 67,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,21; 155,77</t>
+          <t>54,32; 158,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 39,28</t>
+          <t>-13,25; 37,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,23; 87,49</t>
+          <t>19,31; 89,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,25; 155,26</t>
+          <t>94,83; 185,3</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>9,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>6,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,4</t>
+          <t>-2,59; 3,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,03</t>
+          <t>1,88; 8,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,69</t>
+          <t>5,93; 13,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,19</t>
+          <t>-5,07; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,44</t>
+          <t>-1,34; 5,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 4,22</t>
+          <t>0,1; 6,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,77</t>
+          <t>-2,85; 1,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,91</t>
+          <t>1,13; 6,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 6,73</t>
+          <t>4,03; 8,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110,2%</t>
+          <t>122,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 58,07</t>
+          <t>-28,94; 54,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,73; 143,43</t>
+          <t>19,32; 133,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50,86; 192,49</t>
+          <t>61,97; 211,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 14,69</t>
+          <t>-41,75; 18,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 60,42</t>
+          <t>-10,81; 61,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 44,92</t>
+          <t>0,37; 71,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 22,34</t>
+          <t>-27,8; 19,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,17; 76,21</t>
+          <t>9,46; 75,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 80,97</t>
+          <t>38,78; 113,94</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>11,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>9,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,46</t>
+          <t>-3,23; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,62</t>
+          <t>1,52; 7,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,54</t>
+          <t>4,13; 10,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,44</t>
+          <t>0,74; 6,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,54</t>
+          <t>5,17; 11,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,38</t>
+          <t>8,41; 13,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,64</t>
+          <t>-0,24; 3,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,72</t>
+          <t>4,39; 8,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,08</t>
+          <t>7,05; 11,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>105,54%</t>
+          <t>117,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 30,35</t>
+          <t>-28,17; 30,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,04; 90,62</t>
+          <t>11,67; 86,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,57; 124,23</t>
+          <t>35,01; 120,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 77,13</t>
+          <t>6,0; 79,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,33; 138,55</t>
+          <t>45,8; 135,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,87; 164,42</t>
+          <t>73,49; 169,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 41,6</t>
+          <t>-2,4; 43,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>41,8; 100,38</t>
+          <t>41,17; 98,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60,15; 125,87</t>
+          <t>63,87; 131,71</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>9,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,54</t>
+          <t>-0,24; 2,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,66</t>
+          <t>3,81; 6,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,61</t>
+          <t>9,58; 12,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,8</t>
+          <t>-0,2; 2,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,03</t>
+          <t>2,98; 5,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,26</t>
+          <t>7,38; 10,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,17</t>
+          <t>0,16; 2,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,89</t>
+          <t>3,7; 6,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,87</t>
+          <t>8,86; 10,98</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129,92%</t>
+          <t>152,99%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>100,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>105,1%</t>
+          <t>124,02%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 37,87</t>
+          <t>-3,37; 37,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43,69; 99,09</t>
+          <t>47,44; 103,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>77,09; 173,62</t>
+          <t>120,91; 200,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 33,83</t>
+          <t>-2,48; 33,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>32,11; 76,08</t>
+          <t>31,07; 74,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,65; 113,27</t>
+          <t>77,37; 127,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,68; 28,73</t>
+          <t>1,79; 28,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>44,08; 77,76</t>
+          <t>42,87; 79,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>75,34; 128,64</t>
+          <t>103,32; 145,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
